--- a/output/2026-09-01_06_Italia_Umbria_ATEX_Equipment_Services.xlsx
+++ b/output/2026-09-01_06_Italia_Umbria_ATEX_Equipment_Services.xlsx
@@ -498,7 +498,6 @@
           <t>0744 813485</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Sito con pagine dedicate a impianti elettrici antideflagranti ATEX; attiva dal 1971 nel settore chimico/petrolchimico/energia.</t>
@@ -578,7 +577,6 @@
           <t>075 8000848 / 075 8010295 / 347 9234477</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Oltre 40 anni in impianti elettrici industriali; offre sistemi ATEX per l'industria (P.IVA 01545490540).</t>
@@ -623,7 +621,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dal 1982 specializzata in impianti di aspirazione aria industriale, abbattimento polveri/vapori, trasporto polveri.</t>
+          <t>Dal 1982 specializzata in impianti di aspirazione aria industriale, abbattimento polveri/vapori, trasporto polveri. [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -653,11 +651,9 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Officina meccanica, 40 anni di esperienza in impianti di aspirazione, filtrazione, trasportatori e silos industriali.</t>
+          <t>Officina meccanica, 40 anni di esperienza in impianti di aspirazione, filtrazione, trasportatori e silos industriali. [DUPLICATO — vedi anche: 2026-09-01_03_Italia_Umbria_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -692,7 +688,6 @@
           <t>075 8043623</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Oltre 50 anni in impianti per mangimi/pet food e packaging, inclusi trasporto pneumatico/aspirazione polveri (rischio polveri combustibili).</t>
@@ -730,7 +725,6 @@
           <t>075 528561</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Grande distributore di materiale elettrico industriale (Gruppo Comet); catalogo ATEX specifico non confermato, da verificare con contatto diretto.</t>
